--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -432,7 +432,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AI4"/>
+  <dimension ref="A1:AI7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -618,12 +618,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>05:00</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Australia A-League</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -633,12 +633,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Neom SC</t>
+          <t>Central Coast Mariners</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Al Ittihad</t>
+          <t>Brisbane Roar</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>0</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>0</v>
@@ -704,10 +704,10 @@
         <v>0</v>
       </c>
       <c r="AA2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -728,7 +728,7 @@
         <v>0</v>
       </c>
       <c r="AI2" s="3" t="n">
-        <v>46022.51736111111</v>
+        <v>46022.20833333334</v>
       </c>
     </row>
     <row r="3">
@@ -737,12 +737,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14:30</t>
+          <t>09:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Saudi Arabia Professional League</t>
+          <t>Ethiopia Ethiopia Premier League</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -752,12 +752,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Mekelakeya</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Ethiopia Bunna</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -847,7 +847,7 @@
         <v>0</v>
       </c>
       <c r="AI3" s="3" t="n">
-        <v>46022.60416666666</v>
+        <v>46022.375</v>
       </c>
     </row>
     <row r="4">
@@ -856,116 +856,473 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
+          <t>10:00</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>Ethiopia Ethiopia Premier League</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Ethiopia Nigd Bank</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Ethiopian Medhin</t>
+        </is>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="n">
+        <v>0</v>
+      </c>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="n">
+        <v>0</v>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L4" t="n">
+        <v>0</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>0</v>
+      </c>
+      <c r="P4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0</v>
+      </c>
+      <c r="T4" t="n">
+        <v>0</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI4" s="3" t="n">
+        <v>46022.41666666666</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>12:25</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Neom SC</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Al Ittihad</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>0</v>
+      </c>
+      <c r="P5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>0</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="3" t="n">
+        <v>46022.51736111111</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
           <t>14:30</t>
         </is>
       </c>
-      <c r="C4" t="inlineStr">
+      <c r="C6" t="inlineStr">
         <is>
           <t>Saudi Arabia Professional League</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr">
+      <c r="D6" t="inlineStr">
         <is>
           <t>2025/2026</t>
         </is>
       </c>
-      <c r="E4" t="inlineStr">
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Al Kholood</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Al Hilal</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>incomplete</t>
+        </is>
+      </c>
+      <c r="L6" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="3" t="n">
+        <v>46022.60416666666</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>46022</v>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>14:30</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Saudi Arabia Professional League</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
         <is>
           <t>Al Shabab</t>
         </is>
       </c>
-      <c r="F4" t="inlineStr">
+      <c r="F7" t="inlineStr">
         <is>
           <t>Al Quadisiya</t>
         </is>
       </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="n">
-        <v>0</v>
-      </c>
-      <c r="I4" t="n">
-        <v>0</v>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
-      </c>
-      <c r="K4" t="inlineStr">
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" t="inlineStr">
         <is>
           <t>incomplete</t>
         </is>
       </c>
-      <c r="L4" t="n">
-        <v>0</v>
-      </c>
-      <c r="M4" t="n">
-        <v>0</v>
-      </c>
-      <c r="N4" t="n">
-        <v>0</v>
-      </c>
-      <c r="O4" t="n">
-        <v>0</v>
-      </c>
-      <c r="P4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q4" t="n">
-        <v>0</v>
-      </c>
-      <c r="R4" t="n">
-        <v>0</v>
-      </c>
-      <c r="S4" t="n">
-        <v>0</v>
-      </c>
-      <c r="T4" t="n">
-        <v>0</v>
-      </c>
-      <c r="U4" t="n">
-        <v>0</v>
-      </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI4" s="3" t="n">
+      <c r="L7" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>0</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>
       </c>
     </row>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,73 +659,73 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.02</v>
       </c>
       <c r="O2" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="P2" t="n">
-        <v>0</v>
+        <v>2.09</v>
       </c>
       <c r="Q2" t="n">
-        <v>0</v>
+        <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="T2" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="Z2" t="n">
-        <v>0</v>
+        <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2.05</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>0</v>
+        <v>3.56</v>
       </c>
       <c r="AD2" t="n">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46022.20833333334</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.56</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.05</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.56</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.4</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.45</v>
-      </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
         <v>3.56</v>
@@ -680,7 +680,7 @@
         <v>1.38</v>
       </c>
       <c r="S2" t="n">
-        <v>2.88</v>
+        <v>2.85</v>
       </c>
       <c r="T2" t="n">
         <v>2.75</v>
@@ -689,10 +689,10 @@
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>6.85</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.07</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,22 +704,22 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>1.98</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.56</v>
+        <v>3.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="AE2" t="n">
         <v>1.8</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
         <v>1.32</v>
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0</v>
+        <v>3.17</v>
       </c>
       <c r="P5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="R5" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
-        <v>0</v>
+        <v>2.18</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1.6</v>
       </c>
       <c r="V5" t="n">
-        <v>0</v>
+        <v>4.7</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Z5" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AA5" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>2.42</v>
       </c>
       <c r="AC5" t="n">
-        <v>0</v>
+        <v>2.23</v>
       </c>
       <c r="AD5" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
+        <v>2.59</v>
       </c>
       <c r="AG5" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46022.51736111111</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.56</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.98</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -668,19 +668,19 @@
         <v>2.08</v>
       </c>
       <c r="O2" t="n">
-        <v>3.56</v>
+        <v>3.8</v>
       </c>
       <c r="P2" t="n">
-        <v>2.09</v>
+        <v>2.2</v>
       </c>
       <c r="Q2" t="n">
         <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.36</v>
       </c>
       <c r="S2" t="n">
-        <v>2.85</v>
+        <v>2.81</v>
       </c>
       <c r="T2" t="n">
         <v>2.75</v>
@@ -689,10 +689,10 @@
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.85</v>
+        <v>7</v>
       </c>
       <c r="W2" t="n">
-        <v>1.07</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -716,13 +716,13 @@
         <v>1.26</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.8</v>
+        <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="AH2" t="n">
         <v>1.32</v>
@@ -1025,64 +1025,64 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.17</v>
+        <v>3.25</v>
       </c>
       <c r="P5" t="n">
-        <v>2.42</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.51</v>
+        <v>2.54</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="S5" t="n">
-        <v>3.7</v>
+        <v>3.86</v>
       </c>
       <c r="T5" t="n">
-        <v>2.18</v>
+        <v>2.1</v>
       </c>
       <c r="U5" t="n">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="V5" t="n">
-        <v>4.7</v>
+        <v>4.45</v>
       </c>
       <c r="W5" t="n">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.1</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>5</v>
+        <v>5.35</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.42</v>
+        <v>2.56</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.58</v>
+        <v>1.64</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.59</v>
+        <v>2.7</v>
       </c>
       <c r="AG5" t="n">
         <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46022.51736111111</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>3.61</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>3.27</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>0</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>7.9</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>0</v>
+        <v>3.59</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -662,10 +662,10 @@
         <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.46</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.61</v>
+        <v>7.9</v>
       </c>
       <c r="M6" t="n">
-        <v>3.27</v>
+        <v>6</v>
       </c>
       <c r="N6" t="n">
-        <v>2</v>
+        <v>1.21</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>3.59</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.9</v>
+        <v>3.61</v>
       </c>
       <c r="M7" t="n">
-        <v>6</v>
+        <v>3.27</v>
       </c>
       <c r="N7" t="n">
-        <v>1.21</v>
+        <v>2</v>
       </c>
       <c r="O7" t="n">
-        <v>7.91</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
@@ -1055,7 +1055,7 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.09</v>
       </c>
       <c r="Z5" t="n">
         <v>5.35</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.9</v>
+        <v>3.3</v>
       </c>
       <c r="M6" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="N6" t="n">
-        <v>1.21</v>
+        <v>2.05</v>
       </c>
       <c r="O6" t="n">
-        <v>7.91</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3.2</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.58</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.27</v>
+        <v>2.05</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.59</v>
+        <v>1.75</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.76</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.95</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.64</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>3.61</v>
+        <v>11</v>
       </c>
       <c r="M7" t="n">
-        <v>3.27</v>
+        <v>6.2</v>
       </c>
       <c r="N7" t="n">
-        <v>2</v>
+        <v>1.19</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>7.91</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.58</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.86</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.05</v>
+        <v>1.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.75</v>
+        <v>3.59</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.95</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -662,10 +662,10 @@
         <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.46</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>
@@ -1025,58 +1025,58 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="R5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S5" t="n">
-        <v>3.86</v>
+        <v>3.74</v>
       </c>
       <c r="T5" t="n">
-        <v>2.1</v>
+        <v>2.13</v>
       </c>
       <c r="U5" t="n">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>4.45</v>
+        <v>4.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.35</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.56</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="AD5" t="n">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.7</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
         <v>1.18</v>
@@ -1135,10 +1135,10 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.3</v>
+        <v>3.6</v>
       </c>
       <c r="M6" t="n">
-        <v>3</v>
+        <v>3.18</v>
       </c>
       <c r="N6" t="n">
         <v>2.05</v>
@@ -1257,16 +1257,16 @@
         <v>11</v>
       </c>
       <c r="M7" t="n">
-        <v>6.2</v>
+        <v>6.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>7.91</v>
+        <v>7.9</v>
       </c>
       <c r="P7" t="n">
-        <v>3.2</v>
+        <v>3.21</v>
       </c>
       <c r="Q7" t="n">
         <v>1.58</v>
@@ -1278,16 +1278,16 @@
         <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="U7" t="n">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="V7" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
         <v>1.01</v>
@@ -1296,19 +1296,19 @@
         <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.6</v>
+        <v>6.55</v>
       </c>
       <c r="AA7" t="n">
         <v>1.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.59</v>
+        <v>3.42</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.95</v>
+        <v>1.93</v>
       </c>
       <c r="AE7" t="n">
         <v>1.64</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -662,10 +662,10 @@
         <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -662,10 +662,10 @@
         <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -677,7 +677,7 @@
         <v>2.66</v>
       </c>
       <c r="R2" t="n">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="S2" t="n">
         <v>2.81</v>
@@ -713,16 +713,16 @@
         <v>3.24</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AE2" t="n">
         <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.25</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
         <v>1.32</v>
@@ -1031,7 +1031,7 @@
         <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.56</v>
+        <v>2.42</v>
       </c>
       <c r="R5" t="n">
         <v>1.19</v>
@@ -1049,16 +1049,16 @@
         <v>4.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.13</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.2</v>
+        <v>5.35</v>
       </c>
       <c r="AA5" t="n">
         <v>1.46</v>
@@ -1135,13 +1135,13 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>3.6</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>3.18</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>2.05</v>
+        <v>1.77</v>
       </c>
       <c r="O6" t="n">
         <v>0</v>
@@ -1180,10 +1180,10 @@
         <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
         <v>0</v>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>11</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
-        <v>6.05</v>
+        <v>5.85</v>
       </c>
       <c r="N7" t="n">
         <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>7.9</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>3.21</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
         <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>1.83</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
         <v>3.6</v>
@@ -1296,31 +1296,31 @@
         <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.55</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.27</v>
+        <v>1.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.42</v>
+        <v>3.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.64</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.03</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -674,7 +674,7 @@
         <v>2.2</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="R2" t="n">
         <v>1.38</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>
@@ -719,7 +719,7 @@
         <v>1.75</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="AG2" t="n">
         <v>1.32</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>7.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>5.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>5.85</v>
+        <v>3.36</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>4.33</v>
       </c>
       <c r="M6" t="n">
-        <v>5.85</v>
+        <v>3.36</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>7.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.36</v>
+        <v>5.85</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="AB7" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.1</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.03</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.8</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.33</v>
+        <v>7.2</v>
       </c>
       <c r="M6" t="n">
-        <v>3.36</v>
+        <v>5.85</v>
       </c>
       <c r="N6" t="n">
-        <v>1.77</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.5</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>2</v>
+        <v>1.34</v>
       </c>
       <c r="AB6" t="n">
-        <v>1.8</v>
+        <v>3.08</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.2</v>
+        <v>4.33</v>
       </c>
       <c r="M7" t="n">
-        <v>5.85</v>
+        <v>3.36</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.77</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.34</v>
+        <v>2</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.08</v>
+        <v>1.8</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,16 +659,16 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.13</v>
       </c>
       <c r="O2" t="n">
-        <v>3.8</v>
+        <v>3.63</v>
       </c>
       <c r="P2" t="n">
         <v>2.2</v>
@@ -689,7 +689,7 @@
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="W2" t="n">
         <v>1.04</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2.02</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="AC2" t="n">
         <v>3.24</v>
@@ -716,13 +716,13 @@
         <v>1.29</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.6</v>
       </c>
       <c r="AH2" t="n">
         <v>1.32</v>
@@ -1025,7 +1025,7 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.2</v>
+        <v>3.35</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
@@ -1034,10 +1034,10 @@
         <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
-        <v>3.74</v>
+        <v>3.7</v>
       </c>
       <c r="T5" t="n">
         <v>2.13</v>
@@ -1049,22 +1049,22 @@
         <v>4.55</v>
       </c>
       <c r="W5" t="n">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="X5" t="n">
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.35</v>
+        <v>5.37</v>
       </c>
       <c r="AA5" t="n">
         <v>1.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AC5" t="n">
         <v>2.16</v>
@@ -1073,16 +1073,16 @@
         <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46022.51736111111</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>4.87</v>
       </c>
       <c r="M6" t="n">
-        <v>5.85</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.5</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.34</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.08</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.79</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.92</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.63</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>3.85</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.33</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.36</v>
+        <v>6.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.77</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>2</v>
+        <v>1.33</v>
       </c>
       <c r="AB7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.87</v>
+        <v>8.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.5</v>
+        <v>4.87</v>
       </c>
       <c r="M7" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.5</v>
+        <v>4.87</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.87</v>
+        <v>8.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB7" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC7" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB7" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>0</v>
-      </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,31 +659,31 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="M2" t="n">
         <v>3.5</v>
       </c>
       <c r="N2" t="n">
-        <v>2.13</v>
+        <v>2.05</v>
       </c>
       <c r="O2" t="n">
-        <v>3.63</v>
+        <v>4</v>
       </c>
       <c r="P2" t="n">
-        <v>2.2</v>
+        <v>2.21</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.64</v>
+        <v>2.54</v>
       </c>
       <c r="R2" t="n">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="T2" t="n">
         <v>2.81</v>
-      </c>
-      <c r="T2" t="n">
-        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
@@ -692,7 +692,7 @@
         <v>6.9</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,16 +704,16 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.24</v>
+        <v>3.45</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.29</v>
+        <v>1.25</v>
       </c>
       <c r="AE2" t="n">
         <v>1.76</v>
@@ -722,7 +722,7 @@
         <v>1.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="AH2" t="n">
         <v>1.32</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.87</v>
+        <v>8.5</v>
       </c>
       <c r="M6" t="n">
-        <v>3.7</v>
+        <v>6.5</v>
       </c>
       <c r="N6" t="n">
-        <v>1.6</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>6.5</v>
       </c>
       <c r="P6" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.65</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>8.5</v>
+        <v>4.87</v>
       </c>
       <c r="M7" t="n">
-        <v>6.5</v>
+        <v>3.7</v>
       </c>
       <c r="N7" t="n">
-        <v>1.22</v>
+        <v>1.6</v>
       </c>
       <c r="O7" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -662,10 +662,10 @@
         <v>3.4</v>
       </c>
       <c r="M2" t="n">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="N2" t="n">
-        <v>2.05</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>4</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.45</v>
@@ -1025,16 +1025,16 @@
         <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.35</v>
+        <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>2.5</v>
+        <v>2.4</v>
       </c>
       <c r="Q5" t="n">
         <v>2.42</v>
       </c>
       <c r="R5" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S5" t="n">
         <v>3.7</v>
@@ -1055,16 +1055,16 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.37</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.46</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
         <v>2.16</v>
@@ -1073,16 +1073,16 @@
         <v>1.62</v>
       </c>
       <c r="AE5" t="n">
-        <v>1.43</v>
+        <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
         <v>1.19</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.32</v>
+        <v>1.31</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46022.51736111111</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>8.5</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
-        <v>6.5</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>6.5</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.33</v>
+        <v>1.8</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.65</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.87</v>
+        <v>10.5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.7</v>
+        <v>6.9</v>
       </c>
       <c r="N7" t="n">
-        <v>1.6</v>
+        <v>1.12</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>7.65</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>2.89</v>
       </c>
       <c r="Q7" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.14</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,40 +659,40 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
-        <v>4</v>
+        <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.21</v>
+        <v>2.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>2.54</v>
+        <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="S2" t="n">
-        <v>2.9</v>
+        <v>2.77</v>
       </c>
       <c r="T2" t="n">
-        <v>2.81</v>
+        <v>2.75</v>
       </c>
       <c r="U2" t="n">
         <v>1.38</v>
       </c>
       <c r="V2" t="n">
-        <v>6.9</v>
+        <v>6.5</v>
       </c>
       <c r="W2" t="n">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -704,13 +704,13 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.45</v>
+        <v>3.3</v>
       </c>
       <c r="AD2" t="n">
         <v>1.25</v>
@@ -722,10 +722,10 @@
         <v>1.96</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.32</v>
+        <v>1.76</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46022.20833333334</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="M6" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S6" t="n">
         <v>4.15</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AB6" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="M7" t="n">
-        <v>6.9</v>
+        <v>4.15</v>
       </c>
       <c r="N7" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="O7" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" t="n">
         <v>1.8</v>
       </c>
-      <c r="V7" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W7" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X7" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y7" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA7" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AB7" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.45</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.6</v>
@@ -704,10 +704,10 @@
         <v>3.18</v>
       </c>
       <c r="AA2" t="n">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.3</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>7.3</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -817,10 +817,10 @@
         <v>0</v>
       </c>
       <c r="Y3" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>2.77</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -936,10 +936,10 @@
         <v>0</v>
       </c>
       <c r="Y4" t="n">
-        <v>0</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="n">
         <v>0</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10.5</v>
+        <v>5.4</v>
       </c>
       <c r="M6" t="n">
-        <v>6.9</v>
+        <v>4.15</v>
       </c>
       <c r="N6" t="n">
-        <v>1.12</v>
+        <v>1.41</v>
       </c>
       <c r="O6" t="n">
-        <v>7.65</v>
+        <v>0</v>
       </c>
       <c r="P6" t="n">
-        <v>2.89</v>
+        <v>0</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.59</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.8</v>
       </c>
-      <c r="V6" t="n">
-        <v>3.58</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>6.4</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.27</v>
-      </c>
       <c r="AB6" t="n">
-        <v>3.05</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.21</v>
+        <v>0</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5.4</v>
+        <v>10.5</v>
       </c>
       <c r="M7" t="n">
+        <v>6.9</v>
+      </c>
+      <c r="N7" t="n">
+        <v>1.12</v>
+      </c>
+      <c r="O7" t="n">
+        <v>7.65</v>
+      </c>
+      <c r="P7" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="R7" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="S7" t="n">
         <v>4.15</v>
       </c>
-      <c r="N7" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O7" t="n">
-        <v>0</v>
-      </c>
-      <c r="P7" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q7" t="n">
-        <v>0</v>
-      </c>
-      <c r="R7" t="n">
-        <v>0</v>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.58</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.27</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>3.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
+        <v>2.21</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,34 +659,34 @@
         </is>
       </c>
       <c r="L2" t="n">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="M2" t="n">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="N2" t="n">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="O2" t="n">
         <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.07</v>
+        <v>2.06</v>
       </c>
       <c r="Q2" t="n">
         <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="S2" t="n">
-        <v>2.77</v>
+        <v>2.73</v>
       </c>
       <c r="T2" t="n">
         <v>2.75</v>
       </c>
       <c r="U2" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="V2" t="n">
         <v>6.5</v>
@@ -698,16 +698,16 @@
         <v>1.01</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.18</v>
+        <v>3.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>1.85</v>
+        <v>2.06</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.85</v>
+        <v>1.8</v>
       </c>
       <c r="AC2" t="n">
         <v>3.3</v>
@@ -787,64 +787,64 @@
         <v>7.3</v>
       </c>
       <c r="O3" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="P3" t="n">
-        <v>0</v>
+        <v>1.76</v>
       </c>
       <c r="Q3" t="n">
-        <v>0</v>
+        <v>3.76</v>
       </c>
       <c r="R3" t="n">
-        <v>0</v>
+        <v>1.64</v>
       </c>
       <c r="S3" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="T3" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="U3" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V3" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="W3" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>0</v>
+        <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.12</v>
+        <v>2.13</v>
       </c>
       <c r="AA3" t="n">
-        <v>0</v>
+        <v>2.83</v>
       </c>
       <c r="AB3" t="n">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AC3" t="n">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AD3" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE3" t="n">
-        <v>0</v>
+        <v>2.27</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
+        <v>1.54</v>
       </c>
       <c r="AG3" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH3" t="n">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="AI3" s="3" t="n">
         <v>46022.375</v>
@@ -897,73 +897,73 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.77</v>
+        <v>2.95</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94</v>
+        <v>2.7</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>0</v>
+        <v>4.18</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>3.38</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>1.63</v>
       </c>
       <c r="S4" t="n">
-        <v>0</v>
+        <v>2.11</v>
       </c>
       <c r="T4" t="n">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="U4" t="n">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="W4" t="n">
-        <v>0</v>
+        <v>1.03</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.59</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>2.19</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="AB4" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="AC4" t="n">
-        <v>0</v>
+        <v>5.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="AE4" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH4" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46022.41666666666</v>
@@ -1016,25 +1016,25 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="O5" t="n">
         <v>3.48</v>
       </c>
       <c r="P5" t="n">
-        <v>2.4</v>
+        <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.42</v>
+        <v>2.49</v>
       </c>
       <c r="R5" t="n">
-        <v>1.22</v>
+        <v>1.2</v>
       </c>
       <c r="S5" t="n">
         <v>3.7</v>
@@ -1046,7 +1046,7 @@
         <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>4.55</v>
+        <v>4.4</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1055,19 +1055,19 @@
         <v>1.01</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.2</v>
+        <v>5.25</v>
       </c>
       <c r="AA5" t="n">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.49</v>
+        <v>2.61</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="AD5" t="n">
         <v>1.62</v>
@@ -1076,10 +1076,10 @@
         <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="AH5" t="n">
         <v>1.31</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>5.4</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
+        <v>6.05</v>
+      </c>
+      <c r="N6" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="O6" t="n">
+        <v>7</v>
+      </c>
+      <c r="P6" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="R6" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="S6" t="n">
         <v>4.15</v>
       </c>
-      <c r="N6" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="O6" t="n">
-        <v>0</v>
-      </c>
-      <c r="P6" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
-      <c r="R6" t="n">
-        <v>0</v>
-      </c>
-      <c r="S6" t="n">
-        <v>0</v>
-      </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="AB6" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="AC6" t="n">
         <v>1.8</v>
       </c>
-      <c r="AB6" t="n">
-        <v>2</v>
-      </c>
-      <c r="AC6" t="n">
-        <v>0</v>
-      </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>0</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>10.5</v>
+        <v>4.96</v>
       </c>
       <c r="M7" t="n">
-        <v>6.9</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.12</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>7.65</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>2.89</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.59</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.14</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.58</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.09</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.27</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.05</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.21</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.03</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -817,16 +817,16 @@
         <v>1.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.13</v>
+        <v>2.12</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.83</v>
+        <v>3.09</v>
       </c>
       <c r="AB3" t="n">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="AC3" t="n">
         <v>5.7</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.95</v>
+        <v>2.77</v>
       </c>
       <c r="M4" t="n">
-        <v>2.7</v>
+        <v>1.94</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>4.3</v>
       </c>
       <c r="O4" t="n">
         <v>4.18</v>
@@ -936,16 +936,16 @@
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.59</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.19</v>
+        <v>2.3</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.74</v>
+        <v>2.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
         <v>5.6</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>4.96</v>
       </c>
       <c r="M6" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.96</v>
+        <v>7.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -659,13 +659,13 @@
         </is>
       </c>
       <c r="L2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M2" t="n">
         <v>3.45</v>
       </c>
-      <c r="M2" t="n">
-        <v>3.35</v>
-      </c>
       <c r="N2" t="n">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="O2" t="n">
         <v>3.6</v>
@@ -704,10 +704,10 @@
         <v>3.12</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.06</v>
+        <v>1.85</v>
       </c>
       <c r="AB2" t="n">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="AC2" t="n">
         <v>3.3</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.96</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.7</v>
+        <v>4.96</v>
       </c>
       <c r="M7" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>4.96</v>
       </c>
       <c r="M6" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.96</v>
+        <v>7.7</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -778,34 +778,34 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.7</v>
+        <v>2.8</v>
       </c>
       <c r="M3" t="n">
-        <v>1.66</v>
+        <v>2.6</v>
       </c>
       <c r="N3" t="n">
-        <v>7.3</v>
+        <v>2.75</v>
       </c>
       <c r="O3" t="n">
-        <v>3.45</v>
+        <v>3.54</v>
       </c>
       <c r="P3" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="Q3" t="n">
-        <v>3.76</v>
+        <v>3.86</v>
       </c>
       <c r="R3" t="n">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="S3" t="n">
-        <v>2.1</v>
+        <v>2.05</v>
       </c>
       <c r="T3" t="n">
-        <v>3.88</v>
+        <v>3.94</v>
       </c>
       <c r="U3" t="n">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="V3" t="n">
         <v>10</v>
@@ -814,34 +814,34 @@
         <v>1.02</v>
       </c>
       <c r="X3" t="n">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="Z3" t="n">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>3.09</v>
+        <v>2.88</v>
       </c>
       <c r="AB3" t="n">
         <v>1.32</v>
       </c>
       <c r="AC3" t="n">
-        <v>5.7</v>
+        <v>5.75</v>
       </c>
       <c r="AD3" t="n">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="AE3" t="n">
-        <v>2.27</v>
+        <v>2.29</v>
       </c>
       <c r="AF3" t="n">
-        <v>1.54</v>
+        <v>1.53</v>
       </c>
       <c r="AG3" t="n">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="AH3" t="n">
         <v>1.37</v>
@@ -897,22 +897,22 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>2.77</v>
+        <v>3.2</v>
       </c>
       <c r="M4" t="n">
-        <v>1.94</v>
+        <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>4.3</v>
+        <v>2.45</v>
       </c>
       <c r="O4" t="n">
-        <v>4.18</v>
+        <v>4.41</v>
       </c>
       <c r="P4" t="n">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q4" t="n">
-        <v>3.38</v>
+        <v>3.22</v>
       </c>
       <c r="R4" t="n">
         <v>1.63</v>
@@ -921,13 +921,13 @@
         <v>2.11</v>
       </c>
       <c r="T4" t="n">
-        <v>3.85</v>
+        <v>3.82</v>
       </c>
       <c r="U4" t="n">
         <v>1.18</v>
       </c>
       <c r="V4" t="n">
-        <v>9.199999999999999</v>
+        <v>12</v>
       </c>
       <c r="W4" t="n">
         <v>1.03</v>
@@ -936,19 +936,19 @@
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.3</v>
+        <v>2.21</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="AC4" t="n">
-        <v>5.6</v>
+        <v>5.75</v>
       </c>
       <c r="AD4" t="n">
         <v>1.08</v>
@@ -960,10 +960,10 @@
         <v>1.57</v>
       </c>
       <c r="AG4" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AH4" t="n">
-        <v>1.3</v>
+        <v>1.26</v>
       </c>
       <c r="AI4" s="3" t="n">
         <v>46022.41666666666</v>
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>4.96</v>
+        <v>7.7</v>
       </c>
       <c r="M6" t="n">
-        <v>3.75</v>
+        <v>6.05</v>
       </c>
       <c r="N6" t="n">
-        <v>1.56</v>
+        <v>1.2</v>
       </c>
       <c r="O6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="P6" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>2.1</v>
+        <v>1.57</v>
       </c>
       <c r="R6" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>0</v>
+        <v>4.15</v>
       </c>
       <c r="T6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="W6" t="n">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="Z6" t="n">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.05</v>
+        <v>3.25</v>
       </c>
       <c r="AC6" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.83</v>
+        <v>1.66</v>
       </c>
       <c r="AF6" t="n">
-        <v>1.83</v>
+        <v>2.07</v>
       </c>
       <c r="AG6" t="n">
-        <v>0</v>
+        <v>4.16</v>
       </c>
       <c r="AH6" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>7.7</v>
+        <v>4.96</v>
       </c>
       <c r="M7" t="n">
-        <v>6.05</v>
+        <v>3.75</v>
       </c>
       <c r="N7" t="n">
-        <v>1.2</v>
+        <v>1.56</v>
       </c>
       <c r="O7" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="P7" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.57</v>
+        <v>2.1</v>
       </c>
       <c r="R7" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>4.15</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="V7" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="AB7" t="n">
-        <v>3.25</v>
+        <v>2.05</v>
       </c>
       <c r="AC7" t="n">
-        <v>1.8</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.66</v>
+        <v>1.83</v>
       </c>
       <c r="AF7" t="n">
-        <v>2.07</v>
+        <v>1.83</v>
       </c>
       <c r="AG7" t="n">
-        <v>4.16</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -671,28 +671,28 @@
         <v>3.6</v>
       </c>
       <c r="P2" t="n">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="Q2" t="n">
         <v>2.7</v>
       </c>
       <c r="R2" t="n">
-        <v>1.4</v>
+        <v>1.35</v>
       </c>
       <c r="S2" t="n">
-        <v>2.73</v>
+        <v>3.1</v>
       </c>
       <c r="T2" t="n">
-        <v>2.75</v>
+        <v>2.69</v>
       </c>
       <c r="U2" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="V2" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="W2" t="n">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="X2" t="n">
         <v>1.01</v>
@@ -701,7 +701,7 @@
         <v>1.28</v>
       </c>
       <c r="Z2" t="n">
-        <v>3.12</v>
+        <v>3.38</v>
       </c>
       <c r="AA2" t="n">
         <v>1.85</v>
@@ -710,22 +710,22 @@
         <v>1.85</v>
       </c>
       <c r="AC2" t="n">
-        <v>3.3</v>
+        <v>2.99</v>
       </c>
       <c r="AD2" t="n">
-        <v>1.25</v>
+        <v>1.3</v>
       </c>
       <c r="AE2" t="n">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="AF2" t="n">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="AG2" t="n">
-        <v>1.76</v>
+        <v>1.31</v>
       </c>
       <c r="AH2" t="n">
-        <v>1.28</v>
+        <v>1.31</v>
       </c>
       <c r="AI2" s="3" t="n">
         <v>46022.20833333334</v>
@@ -778,13 +778,13 @@
         </is>
       </c>
       <c r="L3" t="n">
-        <v>2.8</v>
+        <v>2.7</v>
       </c>
       <c r="M3" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="N3" t="n">
-        <v>2.75</v>
+        <v>3</v>
       </c>
       <c r="O3" t="n">
         <v>3.54</v>
@@ -817,13 +817,13 @@
         <v>1.11</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.64</v>
+        <v>1.61</v>
       </c>
       <c r="Z3" t="n">
         <v>2.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.88</v>
+        <v>3.09</v>
       </c>
       <c r="AB3" t="n">
         <v>1.32</v>
@@ -897,13 +897,13 @@
         </is>
       </c>
       <c r="L4" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="M4" t="n">
         <v>2.65</v>
       </c>
       <c r="N4" t="n">
-        <v>2.45</v>
+        <v>2.37</v>
       </c>
       <c r="O4" t="n">
         <v>4.41</v>
@@ -936,16 +936,16 @@
         <v>1.09</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.58</v>
+        <v>1.55</v>
       </c>
       <c r="Z4" t="n">
-        <v>2.21</v>
+        <v>2.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="AB4" t="n">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="AC4" t="n">
         <v>5.75</v>
@@ -1016,22 +1016,22 @@
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="M5" t="n">
-        <v>3.65</v>
+        <v>3.85</v>
       </c>
       <c r="N5" t="n">
-        <v>1.9</v>
+        <v>2.04</v>
       </c>
       <c r="O5" t="n">
-        <v>3.48</v>
+        <v>3.57</v>
       </c>
       <c r="P5" t="n">
         <v>2.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.49</v>
+        <v>2.45</v>
       </c>
       <c r="R5" t="n">
         <v>1.2</v>
@@ -1046,7 +1046,7 @@
         <v>1.63</v>
       </c>
       <c r="V5" t="n">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="W5" t="n">
         <v>1.13</v>
@@ -1058,16 +1058,16 @@
         <v>1.14</v>
       </c>
       <c r="Z5" t="n">
-        <v>5.25</v>
+        <v>5.2</v>
       </c>
       <c r="AA5" t="n">
         <v>1.42</v>
       </c>
       <c r="AB5" t="n">
-        <v>2.61</v>
+        <v>2.49</v>
       </c>
       <c r="AC5" t="n">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="AD5" t="n">
         <v>1.62</v>
@@ -1076,13 +1076,13 @@
         <v>1.41</v>
       </c>
       <c r="AF5" t="n">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="AG5" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="AI5" s="3" t="n">
         <v>46022.51736111111</v>
@@ -1135,28 +1135,28 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>10.6</v>
       </c>
       <c r="M6" t="n">
-        <v>6.05</v>
+        <v>6.8</v>
       </c>
       <c r="N6" t="n">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="O6" t="n">
-        <v>7</v>
+        <v>7.95</v>
       </c>
       <c r="P6" t="n">
         <v>3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.57</v>
+        <v>1.54</v>
       </c>
       <c r="R6" t="n">
         <v>1.16</v>
       </c>
       <c r="S6" t="n">
-        <v>4.15</v>
+        <v>4.1</v>
       </c>
       <c r="T6" t="n">
         <v>1.9</v>
@@ -1165,40 +1165,40 @@
         <v>1.8</v>
       </c>
       <c r="V6" t="n">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="W6" t="n">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="X6" t="n">
         <v>1.01</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="Z6" t="n">
-        <v>6.4</v>
+        <v>7.5</v>
       </c>
       <c r="AA6" t="n">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="AB6" t="n">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.07</v>
+        <v>2.01</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.16</v>
+        <v>1.06</v>
       </c>
       <c r="AH6" t="n">
         <v>1.02</v>
@@ -1254,13 +1254,13 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.96</v>
+        <v>5</v>
       </c>
       <c r="M7" t="n">
-        <v>3.75</v>
+        <v>3.95</v>
       </c>
       <c r="N7" t="n">
-        <v>1.56</v>
+        <v>1.47</v>
       </c>
       <c r="O7" t="n">
         <v>5</v>
@@ -1299,10 +1299,10 @@
         <v>0</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.75</v>
+        <v>1.8</v>
       </c>
       <c r="AB7" t="n">
-        <v>2.05</v>
+        <v>2</v>
       </c>
       <c r="AC7" t="n">
         <v>0</v>

--- a/jogos_2025-12-31.xlsx
+++ b/jogos_2025-12-31.xlsx
@@ -642,20 +642,20 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L2" t="n">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Al Kholood</t>
+          <t>Al Shabab</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Al Hilal</t>
+          <t>Al Quadisiya</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1135,73 +1135,73 @@
         </is>
       </c>
       <c r="L6" t="n">
-        <v>10.6</v>
+        <v>5</v>
       </c>
       <c r="M6" t="n">
-        <v>6.8</v>
+        <v>3.95</v>
       </c>
       <c r="N6" t="n">
-        <v>1.22</v>
+        <v>1.47</v>
       </c>
       <c r="O6" t="n">
-        <v>7.95</v>
+        <v>5</v>
       </c>
       <c r="P6" t="n">
-        <v>3</v>
+        <v>2.3</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.54</v>
+        <v>2.1</v>
       </c>
       <c r="R6" t="n">
-        <v>1.16</v>
+        <v>0</v>
       </c>
       <c r="S6" t="n">
-        <v>4.1</v>
+        <v>0</v>
       </c>
       <c r="T6" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="U6" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" t="n">
         <v>1.8</v>
       </c>
-      <c r="V6" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="W6" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="X6" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="Y6" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="Z6" t="n">
-        <v>7.5</v>
-      </c>
-      <c r="AA6" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AB6" t="n">
-        <v>3.4</v>
+        <v>2</v>
       </c>
       <c r="AC6" t="n">
-        <v>1.81</v>
+        <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>1.89</v>
+        <v>0</v>
       </c>
       <c r="AE6" t="n">
-        <v>1.7</v>
+        <v>1.83</v>
       </c>
       <c r="AF6" t="n">
-        <v>2.01</v>
+        <v>1.83</v>
       </c>
       <c r="AG6" t="n">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="AH6" t="n">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="3" t="n">
         <v>46022.60416666666</v>
@@ -1228,12 +1228,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Al Shabab</t>
+          <t>Al Kholood</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Al Quadisiya</t>
+          <t>Al Hilal</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1254,73 +1254,73 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>5</v>
+        <v>10.6</v>
       </c>
       <c r="M7" t="n">
-        <v>3.95</v>
+        <v>6.8</v>
       </c>
       <c r="N7" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="O7" t="n">
-        <v>5</v>
+        <v>7.95</v>
       </c>
       <c r="P7" t="n">
-        <v>2.3</v>
+        <v>3</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.1</v>
+        <v>1.54</v>
       </c>
       <c r="R7" t="n">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="S7" t="n">
-        <v>0</v>
+        <v>4.1</v>
       </c>
       <c r="T7" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="U7" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="V7" t="n">
-        <v>0</v>
+        <v>3.75</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="Y7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="Z7" t="n">
-        <v>0</v>
+        <v>7.5</v>
       </c>
       <c r="AA7" t="n">
-        <v>1.8</v>
+        <v>1.3</v>
       </c>
       <c r="AB7" t="n">
-        <v>2</v>
+        <v>3.4</v>
       </c>
       <c r="AC7" t="n">
-        <v>0</v>
+        <v>1.81</v>
       </c>
       <c r="AD7" t="n">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="AE7" t="n">
-        <v>1.83</v>
+        <v>1.7</v>
       </c>
       <c r="AF7" t="n">
-        <v>1.83</v>
+        <v>2.01</v>
       </c>
       <c r="AG7" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="AH7" t="n">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="AI7" s="3" t="n">
         <v>46022.60416666666</v>
